--- a/proposal/SAAS_PRICING_JP.xlsx
+++ b/proposal/SAAS_PRICING_JP.xlsx
@@ -13,19 +13,7 @@
     <sheet name="5年TCO比較" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="オプション" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="store_count">見積シミュレーション!$C$6</definedName>
-    <definedName name="plan_choice">見積シミュレーション!$C$7</definedName>
-    <definedName name="price_starter">見積シミュレーション!$C$8</definedName>
-    <definedName name="price_business">見積シミュレーション!$C$9</definedName>
-    <definedName name="price_enterprise">見積シミュレーション!$C$10</definedName>
-    <definedName name="hq_license">見積シミュレーション!$C$11</definedName>
-    <definedName name="init_starter">見積シミュレーション!$C$12</definedName>
-    <definedName name="init_business">見積シミュレーション!$C$13</definedName>
-    <definedName name="init_enterprise">見積シミュレーション!$C$14</definedName>
-    <definedName name="annual_discount">見積シミュレーション!$C$15</definedName>
-    <definedName name="contract_years">見積シミュレーション!$C$16</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="&quot;¥&quot;#,##0;[Red]-&quot;¥&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.00&quot;倍&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,12 +82,6 @@
       <b val="1"/>
       <color rgb="00047857"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Yu Gothic"/>
-      <b val="1"/>
-      <color rgb="00047857"/>
-      <sz val="13"/>
     </font>
     <font>
       <name val="Yu Gothic"/>
@@ -216,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -256,16 +238,10 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -756,7 +732,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>自社開発 (中堅 IT / 大手 SIer) vs WorkBridge SaaS の 5 年総額比較</t>
+          <t>自社開発 (中堅 IT / 大手 SIer) vs SaaS の 5 年総額比較</t>
         </is>
       </c>
       <c r="D13" s="7" t="n"/>
@@ -892,7 +868,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -1114,7 +1090,7 @@
         </is>
       </c>
       <c r="C21" s="18">
-        <f>$C$6*C20</f>
+        <f>$C$6*$C$20</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1112,7 @@
         </is>
       </c>
       <c r="C23" s="19">
-        <f>C21+C22</f>
+        <f>$C$21+$C$22</f>
         <v/>
       </c>
     </row>
@@ -1147,7 +1123,7 @@
         </is>
       </c>
       <c r="C24" s="18">
-        <f>C23*$C$15</f>
+        <f>$C$23*$C$15</f>
         <v/>
       </c>
     </row>
@@ -1157,8 +1133,8 @@
           <t>月額 (年間契約割引適用後)</t>
         </is>
       </c>
-      <c r="C25" s="20">
-        <f>C23-C24</f>
+      <c r="C25" s="19">
+        <f>$C$23-$C$24</f>
         <v/>
       </c>
     </row>
@@ -1168,8 +1144,8 @@
           <t>年額 (税抜・割引後)</t>
         </is>
       </c>
-      <c r="C26" s="20">
-        <f>C25*12</f>
+      <c r="C26" s="19">
+        <f>$C$25*12</f>
         <v/>
       </c>
     </row>
@@ -1190,8 +1166,8 @@
           <t>契約年数の総額 (税抜)</t>
         </is>
       </c>
-      <c r="C28" s="21">
-        <f>C26*$C$16+C27</f>
+      <c r="C28" s="19">
+        <f>$C$26*$C$16+$C$27</f>
         <v/>
       </c>
     </row>
@@ -1247,858 +1223,858 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Starter</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Enterprise</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>月額/店舗 (税抜)</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>¥12,800</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>¥9,800</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>¥6,800〜</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>本部ライセンス/月</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>¥80,000〜¥150,000</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>初期費用</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>¥150,000</t>
         </is>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>¥300,000</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
-        <is>
-          <t>¥0〜¥2,000,000 (規模協議)</t>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>¥800,000 (規模協議)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>最低契約期間</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>3 ヶ月</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>6 ヶ月</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>12 ヶ月 (年間契約割引 10〜20%)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>対象店舗数</t>
         </is>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>単独店舗のみ</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>1〜5 店舗</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>10 店舗以上</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>スタッフ登録/店舗</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>〜10 名</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>〜20 名</t>
         </is>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>無制限</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>月間翻訳 API 字数</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>50 万字</t>
         </is>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>200 万字/店舗</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>Fair Use 無制限</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>超過課金</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>¥1,000/10 万字</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>¥800/10 万字</t>
         </is>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>リアルタイム指示送受信</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>6 言語自動翻訳</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>やさしい日本語変換</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>3 ボタン応答 + カスタム音声応答</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>画像添付指示</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>CSV 一括登録</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>60 日分の履歴保持</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>選択により最大 12 ヶ月</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>PWA (iOS/Android 対応)</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>店舗専用業務用語辞書</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D21" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>表現・言い換え辞書</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>店舗別ロゴ・ブランド統合</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>オプション</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>標準</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>本部一括ダッシュボード</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>複数店舗一斉指示</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>店舗別 売上・稼働分析</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="E26" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>SSO (SAML/OIDC)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>監査ログ</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E28" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>DB 行レベル分離 (Postgres RLS)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>メールサポート</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E30" s="26" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>チャットサポート</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D31" s="24" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>電話サポート</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E32" s="26" t="inlineStr">
+      <c r="E32" s="24" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>専任カスタマーサクセス</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D33" s="24" t="inlineStr">
+      <c r="D33" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E33" s="22" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="25" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>応答時間 (営業時間内)</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>4 時間</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D34" s="24" t="inlineStr">
         <is>
           <t>2 時間</t>
         </is>
       </c>
-      <c r="E34" s="26" t="inlineStr">
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>1 時間 (重大障害 24h)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>稼働率目標 (SLA)</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="22" t="inlineStr">
         <is>
           <t>ベストエフォート</t>
         </is>
       </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="D35" s="22" t="inlineStr">
         <is>
           <t>99.5%</t>
         </is>
       </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="22" t="inlineStr">
         <is>
           <t>99.9% + 障害時クレジット</t>
         </is>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="25" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>バックアップ</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>日次/7 日</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>日次/14 日</t>
         </is>
       </c>
-      <c r="E36" s="26" t="inlineStr">
+      <c r="E36" s="24" t="inlineStr">
         <is>
           <t>日次/30 日 + オンデマンド</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="B37" s="23" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>オンライントレーニング</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="22" t="inlineStr">
         <is>
           <t>1 回 (1 時間)</t>
         </is>
       </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>2 回 (各 1 時間)</t>
         </is>
       </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="22" t="inlineStr">
         <is>
           <t>無制限</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>オンサイトトレーニング</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>別途有料</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D38" s="24" t="inlineStr">
         <is>
           <t>別途有料</t>
         </is>
       </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="E38" s="24" t="inlineStr">
         <is>
           <t>1 日含む</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="B39" s="23" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>ペネトレーションテスト</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="D39" s="24" t="inlineStr">
+      <c r="D39" s="22" t="inlineStr">
         <is>
           <t>─</t>
         </is>
       </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E39" s="22" t="inlineStr">
         <is>
           <t>年 1 回含む</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B40" s="23" t="inlineStr">
         <is>
           <t>データ削除 SLA</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C40" s="24" t="inlineStr">
         <is>
           <t>5 営業日</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>5 営業日</t>
         </is>
       </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="E40" s="24" t="inlineStr">
         <is>
           <t>2 営業日</t>
         </is>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="23" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>DPA / 個人情報チェックシート</t>
         </is>
       </c>
-      <c r="C41" s="24" t="inlineStr">
+      <c r="C41" s="22" t="inlineStr">
         <is>
           <t>標準</t>
         </is>
       </c>
-      <c r="D41" s="24" t="inlineStr">
+      <c r="D41" s="22" t="inlineStr">
         <is>
           <t>標準 + カスタム項目</t>
         </is>
       </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E41" s="22" t="inlineStr">
         <is>
           <t>個別協議 + DPIA</t>
         </is>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>ホスティング</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="C42" s="24" t="inlineStr">
         <is>
           <t>日本 (東京)</t>
         </is>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D42" s="24" t="inlineStr">
         <is>
           <t>日本 (東京)</t>
         </is>
       </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>日本 (東京) + 専用環境オプション</t>
         </is>
@@ -2129,12 +2105,12 @@
     <row r="2">
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>自社開発 vs WorkBridge SaaS — 5 年総コスト比較</t>
+          <t>自社開発 vs SaaS — 5 年総コスト比較</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>前提: 50 店舗チェーン、5 年運用</t>
         </is>
@@ -2210,7 +2186,7 @@
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>WorkBridge Enterprise 月額/店舗 (¥)</t>
+          <t>WorkBridge Japan Enterprise 月額/店舗 (¥)</t>
         </is>
       </c>
       <c r="C13" s="16" t="n">
@@ -2220,7 +2196,7 @@
     <row r="14">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>WorkBridge Enterprise 本部/月 (¥)</t>
+          <t>WorkBridge Japan Enterprise 本部/月 (¥)</t>
         </is>
       </c>
       <c r="C14" s="16" t="n">
@@ -2230,7 +2206,7 @@
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>WorkBridge 初期費 (¥)</t>
+          <t>SaaS 初期費 (¥)</t>
         </is>
       </c>
       <c r="C15" s="16" t="n">
@@ -2245,80 +2221,80 @@
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>形態</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>初期費用</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>年間運用費 × N</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>5 年総額</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>自社開発 (中堅 IT 会社)</t>
         </is>
       </c>
       <c r="C19" s="18">
-        <f>C9</f>
+        <f>$C$9</f>
         <v/>
       </c>
       <c r="D19" s="18">
-        <f>C10*C8</f>
+        <f>$C$10*$C$8</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="26">
         <f>C19+D19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>自社開発 (大手 SIer)</t>
         </is>
       </c>
       <c r="C20" s="18">
-        <f>C11</f>
+        <f>$C$11</f>
         <v/>
       </c>
       <c r="D20" s="18">
-        <f>C12*C8</f>
+        <f>$C$12*$C$8</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="26">
         <f>C20+D20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="29" t="inlineStr">
-        <is>
-          <t>WorkBridge SaaS (Enterprise)</t>
-        </is>
-      </c>
-      <c r="C21" s="30">
-        <f>C15</f>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>WorkBridge Japan SaaS (Enterprise)</t>
+        </is>
+      </c>
+      <c r="C21" s="28">
+        <f>$C$15</f>
         <v/>
       </c>
-      <c r="D21" s="30">
-        <f>(C13*C7+C14)*12*C8</f>
+      <c r="D21" s="28">
+        <f>($C$13*$C$7+$C$14)*12*$C$8</f>
         <v/>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="19">
         <f>C21+D21</f>
         <v/>
       </c>
@@ -2331,23 +2307,23 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>中堅 IT 開発 / WorkBridge SaaS</t>
-        </is>
-      </c>
-      <c r="C24" s="31">
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>中堅 IT 開発 / WorkBridge Japan SaaS</t>
+        </is>
+      </c>
+      <c r="C24" s="29">
         <f>E19/E21</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>大手 SIer 開発 / WorkBridge SaaS</t>
-        </is>
-      </c>
-      <c r="C25" s="31">
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>大手 SIer 開発 / WorkBridge Japan SaaS</t>
+        </is>
+      </c>
+      <c r="C25" s="29">
         <f>E20/E21</f>
         <v/>
       </c>
@@ -2357,7 +2333,7 @@
         <is>
           <t>※ 中堅 IT 開発の年間運用費は、サーバ運用・保守エンジニア 1〜2 名分を想定。
 ※ 大手 SIer は運用も SLA 付き保守契約での想定。
-※ WorkBridge SaaS の年間運用費には、機能改善・セキュリティアップデート・サポート全て含む。</t>
+※ SaaS の年間運用費には、機能改善・セキュリティアップデート・サポート全て含む。</t>
         </is>
       </c>
     </row>
@@ -2396,34 +2372,34 @@
       </c>
     </row>
     <row r="4" ht="26" customHeight="1">
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>料金 (税抜)</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>標準 6 言語以外の言語追加 (タイ語・タガログ語等)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>初期 ¥100,000 + ¥3,000/月</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>翻訳精度評価込み</t>
         </is>
@@ -2435,29 +2411,29 @@
           <t>カスタム機能開発</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>¥500,000〜</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>規模・要件に応じ個別見積</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="32" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>POS / 勤怠管理 / シフト管理連携</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>¥300,000〜¥2,000,000</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="32" t="inlineStr">
         <is>
           <t>対象システムにより変動</t>
         </is>
@@ -2469,29 +2445,29 @@
           <t>専用ロゴ・ブランド統合</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>¥150,000 (一括)</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>管理者・スタッフ画面</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>オンサイトサポート (店舗訪問)</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>¥150,000/日</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr">
         <is>
           <t>交通費別</t>
         </is>
@@ -2503,29 +2479,29 @@
           <t>プレミアム SLA (24 時間緊急対応)</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>¥150,000/月</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>Enterprise の標準オプション</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>月次定例ミーティング・改善レポート</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>¥50,000/月</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="32" t="inlineStr">
         <is>
           <t>Enterprise 既定</t>
         </is>
@@ -2537,25 +2513,25 @@
           <t>データ保持期間延長 (60 日 → 6 ヶ月)</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>¥10,000/月</t>
         </is>
       </c>
-      <c r="D12" s="36" t="inlineStr"/>
+      <c r="D12" s="34" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>データ保持期間延長 (60 日 → 12 ヶ月)</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>¥20,000/月</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr"/>
+      <c r="D13" s="32" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="B14" s="6" t="inlineStr">
@@ -2563,29 +2539,29 @@
           <t>ペネトレーションテスト (年 1 回)</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>¥500,000〜¥1,500,000/年</t>
         </is>
       </c>
-      <c r="D14" s="36" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>Enterprise 既定</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>DPIA (データ保護影響評価) 個別実施</t>
         </is>
       </c>
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>¥300,000〜</t>
         </is>
       </c>
-      <c r="D15" s="34" t="inlineStr"/>
+      <c r="D15" s="32" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="B16" s="6" t="inlineStr">
@@ -2593,12 +2569,12 @@
           <t>管理者向けスタッフ教育コンテンツ作成</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>¥200,000〜</t>
         </is>
       </c>
-      <c r="D16" s="36" t="inlineStr">
+      <c r="D16" s="34" t="inlineStr">
         <is>
           <t>業種別カリキュラム作成</t>
         </is>
